--- a/pregenereated_results/s2/att_summary_survey.xlsx
+++ b/pregenereated_results/s2/att_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4119231277135923</v>
+        <v>0.4119231277135925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,28 +530,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0355166202146675</v>
+        <v>0.03551662021466816</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3423118312402568</v>
+        <v>0.3423118312402556</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4815344241869278</v>
+        <v>0.4815344241869293</v>
       </c>
       <c r="G2" t="n">
-        <v>4.216315028048566e-31</v>
+        <v>4.216315028059068e-31</v>
       </c>
       <c r="H2" t="n">
-        <v>0.499321025741697</v>
+        <v>0.4993210257416965</v>
       </c>
       <c r="I2" t="n">
-        <v>12.38111981572093</v>
+        <v>12.38111981572091</v>
       </c>
       <c r="J2" t="n">
         <v>3.79917864476386</v>
       </c>
       <c r="K2" t="n">
-        <v>3.380620028518701</v>
+        <v>3.380620028518702</v>
       </c>
       <c r="L2" t="n">
         <v>7220</v>
@@ -560,7 +560,7 @@
         <v>554.8319074166568</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26489450841457e-30</v>
+        <v>1.26489450841772e-30</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04579550992862588</v>
+        <v>-0.04579550992862566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0390974269238337</v>
+        <v>0.03909742692383593</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1224250585875266</v>
+        <v>-0.1224250585875307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03083403873027481</v>
+        <v>0.0308340387302794</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2414710814149033</v>
+        <v>0.2414710814149321</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04256676218162161</v>
+        <v>-0.04256676218162209</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.255616935124911</v>
+        <v>-1.255616935124925</v>
       </c>
       <c r="J3" t="n">
         <v>3.137782340862423</v>
@@ -621,7 +621,7 @@
         <v>554.8319074166568</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2414710814149033</v>
+        <v>0.2414710814149321</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2582177129441011</v>
+        <v>0.2582177129441012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0379034316634053</v>
+        <v>0.03790343166340591</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1839283519933516</v>
+        <v>0.1839283519933505</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3325070738948506</v>
+        <v>0.3325070738948519</v>
       </c>
       <c r="G4" t="n">
-        <v>9.590676754537563e-12</v>
+        <v>9.590676754544794e-12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2951129364911815</v>
+        <v>0.295112936491181</v>
       </c>
       <c r="I4" t="n">
-        <v>9.981897038554889</v>
+        <v>9.981897038554871</v>
       </c>
       <c r="J4" t="n">
         <v>3.061396303901438</v>
@@ -678,7 +678,7 @@
         <v>554.8319074166568</v>
       </c>
       <c r="N4" t="n">
-        <v>1.438601513180635e-11</v>
+        <v>1.438601513181719e-11</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
